--- a/lead-list-builder/demo_output/lead_list.xlsx
+++ b/lead-list-builder/demo_output/lead_list.xlsx
@@ -2079,7 +2079,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-19 20:44</t>
+          <t>2026-10-20 00:45</t>
         </is>
       </c>
     </row>
